--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_IRR.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_IRR.xlsx
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.8657683605759016</v>
+        <v>1.203</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.6926146884607213</v>
+        <v>0.9624000000000001</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.8657683605759016</v>
+        <v>1.203</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>1.038922032691082</v>
+        <v>1.4436</v>
       </c>
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="3" t="inlineStr">
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.4238882496917755</v>
+        <v>0.589</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -2940,13 +2940,13 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.3391105997534204</v>
+        <v>0.4712</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.4238882496917755</v>
+        <v>0.589</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.5086658996301306</v>
+        <v>0.7068</v>
       </c>
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="3" t="inlineStr">
